--- a/output/pdf_financials_xlsx/AU.xlsx
+++ b/output/pdf_financials_xlsx/AU.xlsx
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.096988</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.183204</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -7034,49 +7034,49 @@
         <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.288726</v>
+        <v>-1.146941</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>2.214457</v>
+        <v>1.103502</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.725155</v>
+        <v>-0.213939</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.468156</v>
+        <v>-0.224157</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.784069</v>
+        <v>0.636652</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.011514</v>
+        <v>-0.58304</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.141491</v>
+        <v>-4.160636</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.07625</v>
+        <v>-8.648586</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>1.952118</v>
+        <v>-9.537639</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.457576</v>
+        <v>-8.469645999999999</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.386168</v>
+        <v>-5.50725</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.002078</v>
+        <v>-5.606791</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.198135</v>
+        <v>-3.903329</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-3.762071</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-4.738962</v>
       </c>
     </row>
     <row r="119">
@@ -13198,7 +13198,11 @@
           <t>Share-based payment reserve (Note 12) 815,531</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.096988</v>
       </c>
@@ -14616,7 +14620,11 @@
           <t>Exploration and evaluation expenditures, net</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AU.xlsx
+++ b/output/pdf_financials_xlsx/AU.xlsx
@@ -1008,25 +1008,25 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.028532</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.01149</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.001098</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.003173</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.113363</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.246365</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.233038</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -1897,25 +1897,25 @@
         <v>-3.01468</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.33759</v>
+        <v>-1.366122</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.072916</v>
+        <v>-1.084406</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.321168</v>
+        <v>-1.322266</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.780412</v>
+        <v>-0.783585</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-4.761376</v>
+        <v>-4.874739</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-2.781285</v>
+        <v>-3.02765</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.360492</v>
+        <v>-5.59353</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-2.877371</v>
@@ -2007,25 +2007,25 @@
         <v>-2.979194</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.315703</v>
+        <v>-1.344235</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.066291</v>
+        <v>-1.077781</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.315235</v>
+        <v>-1.316333</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.776822</v>
+        <v>-0.779995</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.732648</v>
+        <v>-4.846011</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-2.682037</v>
+        <v>-2.928402</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.232982</v>
+        <v>-5.46602</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-2.754261</v>
@@ -2304,37 +2304,37 @@
         <v>0.522997</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.011066</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.666662</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>11.769799</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.475556</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>8.750837000000001</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.704898</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>20.300998</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>6.974382</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>5.768561</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>6.494152</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>8.763343000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2414,37 +2414,37 @@
         <v>0.535417</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.036066</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.526748</v>
+        <v>1.19341</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>7.619425</v>
+        <v>19.389224</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>7.625533</v>
+        <v>9.101089</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>3.663824</v>
+        <v>12.414661</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>5.777501</v>
+        <v>7.482399</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>5.018335</v>
+        <v>25.319333</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>2</v>
+        <v>8.974382</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>2.380833</v>
+        <v>8.149393999999999</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>1.258667</v>
+        <v>7.752819</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>1.018</v>
+        <v>9.781343</v>
       </c>
     </row>
     <row r="37">
@@ -3074,37 +3074,37 @@
         <v>0.049293</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.12974</v>
+        <v>0.118674</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.069926</v>
+        <v>0.403264</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>12.423517</v>
+        <v>0.653718</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>2.9317</v>
+        <v>1.456144</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>12.73771</v>
+        <v>3.986873</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>2.201807</v>
+        <v>0.496909</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>20.846487</v>
+        <v>0.545489</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>12.730045</v>
+        <v>5.755663</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>6.408499</v>
+        <v>0.639938</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>6.962462</v>
+        <v>0.46831</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>9.128864999999999</v>
+        <v>0.365522</v>
       </c>
     </row>
     <row r="49">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8270,7 +8270,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>-</t>
@@ -12518,7 +12522,11 @@
           <t>Reclamation deposit -</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.005</v>
       </c>
@@ -14932,7 +14940,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
@@ -25834,7 +25846,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -26416,7 +26428,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -28528,7 +28540,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">

--- a/output/pdf_financials_xlsx/AU.xlsx
+++ b/output/pdf_financials_xlsx/AU.xlsx
@@ -6710,7 +6710,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.016272</v>
       </c>
       <c r="F112" s="3" t="n">
         <v>0</v>
@@ -20392,7 +20392,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AU.xlsx
+++ b/output/pdf_financials_xlsx/AU.xlsx
@@ -6371,52 +6371,52 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-0.132441</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>-0.059663</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
+        <v>0.081261</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>-0.0275</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>0.06289</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.09701799999999999</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>0.032733</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-0.184972</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-0.080209</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-0.655424</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>0.355251</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>0.5546180000000001</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-0.225495</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>-0.149576</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-0.571051</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-0.252442</v>
       </c>
     </row>
     <row r="107">
@@ -6875,22 +6875,22 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.028125</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.02499</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.073891</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.214813</v>
       </c>
       <c r="K115" s="3" t="n">
         <v>0</v>
@@ -6905,10 +6905,10 @@
         <v>0</v>
       </c>
       <c r="O115" s="3" t="n">
-        <v>0</v>
+        <v>1.076255</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.611809</v>
       </c>
       <c r="Q115" s="3" t="n">
         <v>0</v>
@@ -14480,7 +14480,11 @@
           <t>Changes in non-cash operating working capital 15</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -15026,7 +15030,11 @@
           <t>Proceeds from sale of marketable securities 7</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -16690,7 +16698,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -18990,7 +19002,11 @@
           <t>Changes in non-cash operating working capital (Note 12)</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -20978,7 +20994,11 @@
           <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E143" s="5" t="n">
         <v>-0.132441</v>
       </c>
